--- a/data/product_scoring/hersettler_products_list_03-07-2026.xlsx
+++ b/data/product_scoring/hersettler_products_list_03-07-2026.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -154,6 +154,9 @@
     <t xml:space="preserve">#SmoothSkinTexture #TripleElasticity #nonirritating #FirmingAmpoule #Beet #Lychee #VeganMicrobiome</t>
   </si>
   <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hersteller Little Drops Calming Days Ampoule Mask</t>
   </si>
   <si>
@@ -166,6 +169,9 @@
     <t xml:space="preserve">#RapidSoothing #CalmingAmpouleMask #DoubleCalming #nonirritating #VeganBiodegradabilitySheet</t>
   </si>
   <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hersteller Little Drops Calming Days Ampoule Cream</t>
   </si>
   <si>
@@ -185,16 +191,21 @@
   </si>
   <si>
     <t xml:space="preserve">#ClearRadianceAmpoule #ClearSkin #SkinVitalityUP #Improveblemishes #Non-stimulusBrightening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$35.00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="[$$-409]#,##0.00;[RED]\-[$$-409]#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -217,16 +228,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -284,24 +288,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -437,7 +449,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.82"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.84"/>
@@ -445,7 +457,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="13.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="16.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="25.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="25.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="13.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="26.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="20.77"/>
@@ -466,7 +478,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="16.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="15.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="12.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="16.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="16.89"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="37" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -599,6 +611,9 @@
       <c r="F2" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="G2" s="4" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="43.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -613,11 +628,14 @@
       <c r="D3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>43</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="43.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -625,39 +643,45 @@
         <v>1002</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>45</v>
+      <c r="D4" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="56.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>1003</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>49</v>
+      <c r="D5" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -665,19 +689,22 @@
         <v>1004</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
